--- a/DateBase/orders/Nha Thu_2026-6-17.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-17.xlsx
@@ -520,6 +520,9 @@
       <c r="C11" t="str">
         <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -578,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0563.5105752013.50</v>
+        <v>0563.5105752013.510</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-17.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-17.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -524,9 +524,89 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>238_苏菲宝贝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>286_红蕾丝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>226_梦幻芭比_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3</v>
+      </c>
+      <c r="C17" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F17" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F18" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>125_绣球蓝_Hydrangea Light Blue S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F19" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>110_绣球浅蓝_Hydrangea Light Blue S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F20" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>282_绝色果汁_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +661,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0563.5105752013.510</v>
+        <v>0563.5105752013.51088555202015150</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-17.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-17.xlsx
@@ -603,6 +603,9 @@
       <c r="C21" t="str">
         <v>282_绝色果汁_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -661,7 +664,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0563.5105752013.51088555202015150</v>
+        <v>0563.5105752013.51088555202015155</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-17.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-17.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -607,9 +607,92 @@
         <v>5</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>251_暖暖_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>4</v>
+      </c>
+      <c r="C25" t="str">
+        <v>474_掌 黑红色_anthurium_undefined_1bunch</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>5</v>
+      </c>
+      <c r="C26" t="str">
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>771_美洲茶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>1</v>
+      </c>
+      <c r="C28" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>173_朱丽叶_Juliet_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F30" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -664,7 +747,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0563.5105752013.51088555202015155</v>
+        <v>0563.5105752013.510885552020151555550301075150</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-17.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-17.xlsx
@@ -689,6 +689,9 @@
       <c r="C31" t="str">
         <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F31" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -747,7 +750,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0563.5105752013.510885552020151555550301075150</v>
+        <v>0563.5105752013.510885552020151555550301075155</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-17.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-17.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -693,9 +693,89 @@
         <v>5</v>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>143_黑巴克_Black Baccara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>605_康乃馨流光粉_light pink_undefined_20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>200_粉佳人_Nirvana_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2</v>
+      </c>
+      <c r="C35" t="str">
+        <v>152_白荔枝_White Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F35" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>256_奇迹女神_Miracle Goddess_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F36" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>284_可爱瓷_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F37" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F39" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F40" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -750,7 +830,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0563.5105752013.510885552020151555550301075155</v>
+        <v>0563.5105752013.51088555202015155555030107515561055768350</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-17.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-17.xlsx
@@ -772,6 +772,9 @@
       <c r="C41" t="str">
         <v>602_康乃馨白_white_undefined_20stems</v>
       </c>
+      <c r="F41" t="str">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -830,7 +833,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0563.5105752013.51088555202015155555030107515561055768350</v>
+        <v>0563.5105752013.51088555202015155555030107515561055768356</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-17.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-17.xlsx
@@ -711,7 +711,7 @@
     </row>
     <row r="34">
       <c r="C34" t="str">
-        <v>200_粉佳人_Nirvana_Rosa rugosa Thunb._20stems</v>
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
       </c>
       <c r="F34" t="str">
         <v>5</v>

--- a/DateBase/orders/Nha Thu_2026-6-17.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-17.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -776,9 +776,92 @@
         <v>6</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>3</v>
+      </c>
+      <c r="C42" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F42" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F43" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F44" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>287_小粉兔_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F45" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>606_康乃馨橙光_orange_undefined_20stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>611_康乃馨奶油白_cream white_undefined_20stems</v>
+      </c>
+      <c r="F47" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F48" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>4</v>
+      </c>
+      <c r="C49" t="str">
+        <v>286_红蕾丝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F49" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F50" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -833,7 +916,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0563.5105752013.51088555202015155555030107515561055768356</v>
+        <v>0563.5105752013.51088555202015155555030107515561055768356410101255410100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-17.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-17.xlsx
@@ -858,6 +858,9 @@
       <c r="C51" t="str">
         <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F51" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -916,7 +919,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0563.5105752013.51088555202015155555030107515561055768356410101255410100</v>
+        <v>0563.5105752013.51088555202015155555030107515561055768356410101255410105</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-17.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-17.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L71"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -862,9 +862,176 @@
         <v>5</v>
       </c>
     </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>238_苏菲宝贝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F52" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F53" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>281_莱拉_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F54" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>848_吸色康乃馨墨兰_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F55" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>479_绿灵草_lepidium_undefined_1bunch</v>
+      </c>
+      <c r="F56" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>5</v>
+      </c>
+      <c r="C57" t="str">
+        <v>470_海芋白_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F57" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>6</v>
+      </c>
+      <c r="C58" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F58" t="str">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="str">
+        <v>846_玛格丽特_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F59" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="str">
+        <v>468_水仙百合_Alstroemeria_undefined_1bunch</v>
+      </c>
+      <c r="F60" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+      </c>
+      <c r="F61" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" t="str">
+        <v>447_黄金球_craspedia_undefined_1bunch</v>
+      </c>
+      <c r="F62" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>7</v>
+      </c>
+      <c r="C63" t="str">
+        <v>521_商陆_phytolacca acinosa _undefined_1bunch</v>
+      </c>
+      <c r="F63" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" t="str">
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
+      </c>
+      <c r="F64" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" t="str">
+        <v>109_绣球国产绿_Hydrangea Colombia Green (local)_Hydrangea L._1stem</v>
+      </c>
+      <c r="F65" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" t="str">
+        <v>122_绣球拇指薄荷_Hydrangea_Hydrangea L._1stem</v>
+      </c>
+      <c r="F66" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" t="str">
+        <v>125_绣球蓝_Hydrangea Light Blue S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F67" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" xml:space="preserve">
+      <c r="C68" t="str" xml:space="preserve">
+        <v xml:space="preserve">509_翠珠粉_Didiscus caeruleus
+pink_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F68" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" t="str">
+        <v>49_亚丁_Pasta Rosata_Gerbera L._10stems</v>
+      </c>
+      <c r="F69" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" t="str">
+        <v>83_布拉格_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F70" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="str">
+        <v>48_香格里拉_undefined_Gerbera L._10stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L71"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -919,7 +1086,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0563.5105752013.51088555202015155555030107515561055768356410101255410105</v>
+        <v>0563.5105752013.510885552020151555550301075155610557683564101012554101055105205153005555151520203055120</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-17.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-17.xlsx
@@ -1028,6 +1028,9 @@
       <c r="C71" t="str">
         <v>48_香格里拉_undefined_Gerbera L._10stems</v>
       </c>
+      <c r="F71" t="str">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1086,7 +1089,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0563.5105752013.510885552020151555550301075155610557683564101012554101055105205153005555151520203055120</v>
+        <v>0563.5105752013.5108855520201515555503010751556105576835641010125541010551052051530055551515202030551212</v>
       </c>
     </row>
   </sheetData>
